--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_R2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,75 +362,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>LV0_R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>LV1_R2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LV2_R2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LV3_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LV4_R2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LV5_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LV6_R2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LV7_R2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LV8_R2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LV9_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LV10_R2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LV11_R2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV12_R2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LV13_R2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LV14_R2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LV15_R2</t>
         </is>
@@ -443,48 +448,51 @@
         </is>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.3764427531840572</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.5682862867766296</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.6276653861813456</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.6646221451841997</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.7202144488960522</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.740804403280039</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.7500766426527861</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.7536849977290205</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.7704154213941472</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.789618269285256</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.8043013707949513</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.8229987399991232</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.8482121585250829</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.8751998518284875</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0.8912350396960723</v>
       </c>
     </row>
@@ -495,48 +503,51 @@
         </is>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>0.4615252903726945</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.558971599089535</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.6016062466904841</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.6318728135582501</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.6670610172956631</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.70013547074981</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.7318742573682653</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.7535570212966582</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.770375722372152</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.7841486590969873</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.8020378541174974</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.8229054014391817</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.8407220367010841</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.8557845220180029</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0.8702316680241772</v>
       </c>
     </row>
@@ -547,48 +558,51 @@
         </is>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>0.392977851854311</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.5443092686707822</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.5743817914381228</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.6180360253907302</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.6507795885869077</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.6812766797119454</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0.7002347526983254</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.7148958322575685</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.737014456607971</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.7764874640939646</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.8068228145831878</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.8401156612035383</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.8526943610058233</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.8675743907861121</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.8803420375697666</v>
       </c>
     </row>
@@ -599,48 +613,51 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>0.5375709896231395</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.5691128371743177</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.607376998558979</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.6312680578498211</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.674519150163287</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.6947464320955992</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.7127472531983088</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.7462305610570252</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.7801252972592756</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.7931666068867714</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.8145431795359022</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.8366021535140808</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>0.8643343453771178</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.8796030772546167</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.895147703480861</v>
       </c>
     </row>
@@ -651,48 +668,51 @@
         </is>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>0.5386266125730443</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>0.5730591382617127</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.6001540400722326</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.6349828968388485</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.6797687467009197</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.697958718959246</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.7204734548179139</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.7465297446882602</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.7616479822338549</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.7721463130470017</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.7892613576444053</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.8234861040045609</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.8553007970163164</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.8718115127983888</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0.8837104827214988</v>
       </c>
     </row>
@@ -703,48 +723,51 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.391514568334529</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.5580351576659019</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.6605785641571079</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.6919658408741576</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.7340866072588068</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.7390016975081988</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.7515991775145392</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.7653154778191653</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.7832617948790535</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.8141834360483385</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.8404174815240619</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.8541809301059405</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.8724809938662653</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>0.8810450325648281</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>0.8899722482664726</v>
       </c>
     </row>
@@ -755,48 +778,51 @@
         </is>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>0.4440465626248461</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.5359199603128941</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.6154103553175402</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.6536972436379465</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.6640202577352593</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.7046082435562013</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0.7301524651312588</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.758282169039074</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.7832735831620365</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.804062354980453</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.8200261749466966</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.8318272577033483</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.8518389078526818</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.8670775283572651</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>0.8737114591855715</v>
       </c>
     </row>
@@ -807,48 +833,51 @@
         </is>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>0.4440020316488996</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.5358162486003446</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.6141733565994458</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.6505892251665402</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.6596108164008725</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.6943916658552478</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.7175029173157106</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.7281979676619686</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.7418658283031039</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.7580377549648858</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.7679934182472401</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.7755371705657156</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.7917122819002423</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>0.7979704369697289</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>0.8138768237393814</v>
       </c>
     </row>
@@ -859,48 +888,51 @@
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>0.4439626431427508</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.535795339219353</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.6140978815254976</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.6505576629768977</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.6595882999240251</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.6943145499371262</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0.7175967934324541</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.7277224167211522</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.7410627377370624</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.7639060248005574</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.7683943734914924</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.7745619238305772</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.7886136546284688</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.7947388676604322</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>0.8058131128308298</v>
       </c>
     </row>
@@ -911,48 +943,51 @@
         </is>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.4440071184439468</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.5358196977293421</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.6142839721772276</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.650705525854153</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.6596279965693465</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.6947507593117763</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.7173661440004795</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.7290073886579898</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.743027220055501</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.7623679288834333</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.767398055168373</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.775794150212487</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.7928248415259507</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.8054148481481527</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>0.8157330386903646</v>
       </c>
     </row>
@@ -963,48 +998,51 @@
         </is>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0.5469604258189843</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.5806532741154649</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>0.6250093878901746</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.6616092056275795</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.6932678440889837</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.7191511775475283</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.7411501158935193</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.7672239646005531</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.7865479416181257</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.8007630098373888</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.8211836828681274</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.8431402127817167</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.855023754799638</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>0.865564684634052</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0.8812537091032246</v>
       </c>
     </row>
@@ -1015,48 +1053,51 @@
         </is>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0.5485096448293256</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.605891428472237</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.6512772308139381</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.6734525054104656</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.7034086517515592</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.7359313862006587</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.7565906594419011</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.7815959691373546</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.8033770347825036</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.8221203935077063</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.8315657684460113</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.8395600129125826</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.8492380995074783</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.85821995304431</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0.868133889772931</v>
       </c>
     </row>
@@ -1067,48 +1108,51 @@
         </is>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>0.3915054844976599</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.5579695862932501</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>0.6602015877081545</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.6912331619743761</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.732261327218162</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.7366002062032788</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.7463870595156914</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.7546865049985374</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.7657702244617698</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.7763313148909186</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.7975873722392486</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.8118549047724901</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.8265666971186361</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>0.8319328021116863</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0.8373710335361588</v>
       </c>
     </row>
@@ -1119,48 +1163,51 @@
         </is>
       </c>
       <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>0.3914824780383571</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.5580024396892909</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.6602877895145829</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.6913506496973372</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.7323018524868563</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.7365706141988422</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.7461715970741488</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.7541605735461621</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.7646137016995427</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.7727970976434112</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.7910490766091265</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.8048933001410546</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.8184832139270179</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.8236255965832033</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>0.8291406438326664</v>
       </c>
     </row>
@@ -1171,48 +1218,51 @@
         </is>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>0.3914506686016783</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.558009635814237</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.6602560596670235</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.6912849132528509</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.7321508894409952</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.7364262354775317</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.7460409313721841</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.7540386478318868</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.7644951355696619</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.7724719430968083</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.7902131180567202</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.8029717392557353</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.816572572914721</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>0.8216672517452136</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0.8264916742668426</v>
       </c>
     </row>
@@ -1223,48 +1273,51 @@
         </is>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>0.3913725667995176</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.5580262968466154</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.6602488398436399</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.691311007290329</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.732183049572216</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.7364769497843359</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.7460067586148853</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.7538973228760183</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.7644091221253341</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.7728945451805659</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.7909016692384983</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.8042626715589988</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0.8162991914347489</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.8216093069363875</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.8259396283667535</v>
       </c>
     </row>
@@ -1275,48 +1328,51 @@
         </is>
       </c>
       <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>0.5489517456886301</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>0.5834810316825638</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>0.6293891842268833</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.6591889482782001</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.7067382938624147</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.7389540922879978</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.7524178247477863</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.7773685399480416</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.798983770926558</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.8190211863958101</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.8395734116414788</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.8646828482156932</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.8799997981185382</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.8902852016415523</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0.905701815575314</v>
       </c>
     </row>
@@ -1327,48 +1383,51 @@
         </is>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>0.550296619215862</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>0.5885640488251562</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.619796617418112</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.6574366104964229</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.7026861875003723</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.714525059390873</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.7399560082460552</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.770955255935431</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.7876129229124711</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.8056080251118289</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.8227466691660024</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.8451806495474916</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.8591653766397341</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.8702640581705303</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0.8837785738518585</v>
       </c>
     </row>
@@ -1379,48 +1438,51 @@
         </is>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>0.5492078314601765</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>0.5837912981829811</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>0.6355404013569934</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.6744889106002938</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.7019419572219523</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.7156804723465529</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.7458906730121174</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.761750955951022</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.7732538686586751</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.7880065760809487</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.806645454495011</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.8290989852649169</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.8456556277421629</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.8615983587119292</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>0.8770217002291594</v>
       </c>
     </row>
@@ -1431,48 +1493,51 @@
         </is>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>0.460516165067811</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>0.5562821621075118</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.5978726996409082</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.6320629166037337</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.6767943430583268</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.7165268869814649</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.738985191595469</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.7660347379716202</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.7835247095384557</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.7952200181861234</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.8115623176915984</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.8269607827809349</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>0.8421332248461335</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.857178075468513</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0.875156915062046</v>
       </c>
     </row>
@@ -1483,48 +1548,51 @@
         </is>
       </c>
       <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>0.4597193425261389</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>0.5556771610247375</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.5945830609029817</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.6266988088040635</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.6772437201490324</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.7121860394065797</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.7426474612273095</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.7608814951801295</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.7879002888827649</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.797333015933716</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>0.8159774281987064</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.8323434073172582</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>0.8475199858355107</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.8619700292531483</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0.878451695456645</v>
       </c>
     </row>
@@ -1535,1296 +1603,1151 @@
         </is>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>0.5454552239511622</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>0.5788589356432776</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.6148815812802028</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.6250286206477831</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.6521645614983218</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.6928448433881638</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.7299290777915346</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.7566503679830232</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.7815887196447425</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.8158755537113386</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.8447105606390463</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.8647292185967094</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>0.8763978922004649</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.896200306263698</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>0.9122749277716449</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.1464425836074041</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.1947407573395233</v>
+        <v>0.5627320735416819</v>
       </c>
       <c r="D24">
-        <v>0.2190451931662858</v>
+        <v>0.6469237630255931</v>
       </c>
       <c r="E24">
-        <v>0.241944749756591</v>
+        <v>0.6995502516345726</v>
       </c>
       <c r="F24">
-        <v>0.3950975642854401</v>
+        <v>0.7264220033918161</v>
       </c>
       <c r="G24">
-        <v>0.4642902378786017</v>
+        <v>0.73541492436194</v>
       </c>
       <c r="H24">
-        <v>0.5079595550142744</v>
+        <v>0.7464893439354778</v>
       </c>
       <c r="I24">
-        <v>0.5555723044258831</v>
+        <v>0.7641973137077051</v>
       </c>
       <c r="J24">
-        <v>0.6278100677829901</v>
+        <v>0.799459013246499</v>
       </c>
       <c r="K24">
-        <v>0.6583509388278854</v>
+        <v>0.823104470260438</v>
       </c>
       <c r="L24">
-        <v>0.6916997763460501</v>
+        <v>0.8525897157842712</v>
       </c>
       <c r="M24">
-        <v>0.7606862476177726</v>
+        <v>0.8754636467050853</v>
       </c>
       <c r="N24">
-        <v>0.8086848704227326</v>
+        <v>0.8909673755470653</v>
       </c>
       <c r="O24">
-        <v>0.8522846217130279</v>
+        <v>0.9120801450474343</v>
       </c>
       <c r="P24">
-        <v>0.8694102103328376</v>
+        <v>0.9245375866935334</v>
+      </c>
+      <c r="Q24">
+        <v>0.9367777801808277</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.1452234952834593</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.1938266746796268</v>
+        <v>0.5619771539991285</v>
       </c>
       <c r="D25">
-        <v>0.2236065179251563</v>
+        <v>0.6496356782511126</v>
       </c>
       <c r="E25">
-        <v>0.3018356849258688</v>
+        <v>0.7133836538354266</v>
       </c>
       <c r="F25">
-        <v>0.3725335701532423</v>
+        <v>0.7454000318246469</v>
       </c>
       <c r="G25">
-        <v>0.4136410715516178</v>
+        <v>0.7692430952748368</v>
       </c>
       <c r="H25">
-        <v>0.5238374479084157</v>
+        <v>0.7748390316197685</v>
       </c>
       <c r="I25">
-        <v>0.5699022022482133</v>
+        <v>0.7813872232908333</v>
       </c>
       <c r="J25">
-        <v>0.6127272208658445</v>
+        <v>0.8344166784718321</v>
       </c>
       <c r="K25">
-        <v>0.6656082080469231</v>
+        <v>0.8549624558093003</v>
       </c>
       <c r="L25">
-        <v>0.7190458906193857</v>
+        <v>0.86895081679186</v>
       </c>
       <c r="M25">
-        <v>0.7642275115425564</v>
+        <v>0.8867126618793689</v>
       </c>
       <c r="N25">
-        <v>0.8060137469211106</v>
+        <v>0.9022151727716896</v>
       </c>
       <c r="O25">
-        <v>0.8373033982714609</v>
+        <v>0.9209937695973014</v>
       </c>
       <c r="P25">
-        <v>0.8600233197171441</v>
+        <v>0.9300449912232706</v>
+      </c>
+      <c r="Q25">
+        <v>0.9392182853869389</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.1307157914817698</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.1539381349210635</v>
+        <v>0.5764631660922883</v>
       </c>
       <c r="D26">
-        <v>0.1684657216793081</v>
+        <v>0.6330685772366783</v>
       </c>
       <c r="E26">
-        <v>0.2079532783523026</v>
+        <v>0.7070569412800431</v>
       </c>
       <c r="F26">
-        <v>0.2744599565594124</v>
+        <v>0.7220445804087592</v>
       </c>
       <c r="G26">
-        <v>0.3364782502272344</v>
+        <v>0.736347124591711</v>
       </c>
       <c r="H26">
-        <v>0.395442600934193</v>
+        <v>0.7523754403825675</v>
       </c>
       <c r="I26">
-        <v>0.4104329558526778</v>
+        <v>0.7676336153743367</v>
       </c>
       <c r="J26">
-        <v>0.4483479057139373</v>
+        <v>0.7968056776680726</v>
       </c>
       <c r="K26">
-        <v>0.5038045745072249</v>
+        <v>0.836039810683936</v>
       </c>
       <c r="L26">
-        <v>0.5293241328999372</v>
+        <v>0.8767393367235397</v>
       </c>
       <c r="M26">
-        <v>0.5840275371703558</v>
+        <v>0.8938130587526658</v>
       </c>
       <c r="N26">
-        <v>0.6249822484334562</v>
+        <v>0.9105576950976069</v>
       </c>
       <c r="O26">
-        <v>0.6727693621624695</v>
+        <v>0.9245306684909145</v>
       </c>
       <c r="P26">
-        <v>0.6944942766102677</v>
+        <v>0.9366532067854525</v>
+      </c>
+      <c r="Q26">
+        <v>0.9444775845437883</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.1229788547149018</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.1492463073858356</v>
+        <v>0.5764220860086985</v>
       </c>
       <c r="D27">
-        <v>0.2298152685155299</v>
+        <v>0.6326720572452916</v>
       </c>
       <c r="E27">
-        <v>0.2513841642893191</v>
+        <v>0.7061221462369924</v>
       </c>
       <c r="F27">
-        <v>0.3491038294923268</v>
+        <v>0.7188706651289283</v>
       </c>
       <c r="G27">
-        <v>0.4087998697920336</v>
+        <v>0.7320611164060669</v>
       </c>
       <c r="H27">
-        <v>0.450417491331493</v>
+        <v>0.7420822335878672</v>
       </c>
       <c r="I27">
-        <v>0.5031349733842165</v>
+        <v>0.7496198421718681</v>
       </c>
       <c r="J27">
-        <v>0.5838139261442481</v>
+        <v>0.7645618824792639</v>
       </c>
       <c r="K27">
-        <v>0.5962927006741692</v>
+        <v>0.7829413444819477</v>
       </c>
       <c r="L27">
-        <v>0.6273337320323935</v>
+        <v>0.8072883557383186</v>
       </c>
       <c r="M27">
-        <v>0.6822701691266986</v>
+        <v>0.8162365574286319</v>
       </c>
       <c r="N27">
-        <v>0.7078730894020525</v>
+        <v>0.8288031713837667</v>
       </c>
       <c r="O27">
-        <v>0.7409408086336853</v>
+        <v>0.8446875364025619</v>
       </c>
       <c r="P27">
-        <v>0.7636237490808729</v>
+        <v>0.8647898628110134</v>
+      </c>
+      <c r="Q27">
+        <v>0.872386293718881</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.5627320735416819</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.6469237630255931</v>
+        <v>0.561883517829185</v>
       </c>
       <c r="D28">
-        <v>0.6995502516345726</v>
+        <v>0.6492824128193501</v>
       </c>
       <c r="E28">
-        <v>0.7264220033918161</v>
+        <v>0.7123449599378485</v>
       </c>
       <c r="F28">
-        <v>0.73541492436194</v>
+        <v>0.7443660577637363</v>
       </c>
       <c r="G28">
-        <v>0.7464893439354778</v>
+        <v>0.7650825083334859</v>
       </c>
       <c r="H28">
-        <v>0.7641973137077051</v>
+        <v>0.7686383937443441</v>
       </c>
       <c r="I28">
-        <v>0.799459013246499</v>
+        <v>0.7714408147152574</v>
       </c>
       <c r="J28">
-        <v>0.823104470260438</v>
+        <v>0.8026600508391477</v>
       </c>
       <c r="K28">
-        <v>0.8525897157842712</v>
+        <v>0.812263064164377</v>
       </c>
       <c r="L28">
-        <v>0.8754636467050853</v>
+        <v>0.8182323382631078</v>
       </c>
       <c r="M28">
-        <v>0.8909673755470653</v>
+        <v>0.8282229038688391</v>
       </c>
       <c r="N28">
-        <v>0.9120801450474343</v>
+        <v>0.8371239623120978</v>
       </c>
       <c r="O28">
-        <v>0.9245375866935334</v>
+        <v>0.8445600614668181</v>
       </c>
       <c r="P28">
-        <v>0.9367777801808277</v>
+        <v>0.8556317978683903</v>
+      </c>
+      <c r="Q28">
+        <v>0.871586390722342</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.5619771539991285</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.6496356782511126</v>
+        <v>0.5617990615923945</v>
       </c>
       <c r="D29">
-        <v>0.7133836538354266</v>
+        <v>0.64929951493649</v>
       </c>
       <c r="E29">
-        <v>0.7454000318246469</v>
+        <v>0.7122875054296625</v>
       </c>
       <c r="F29">
-        <v>0.7692430952748368</v>
+        <v>0.7444021544193751</v>
       </c>
       <c r="G29">
-        <v>0.7748390316197685</v>
+        <v>0.7649565376607049</v>
       </c>
       <c r="H29">
-        <v>0.7813872232908333</v>
+        <v>0.7685063675896888</v>
       </c>
       <c r="I29">
-        <v>0.8344166784718321</v>
+        <v>0.7712193204482116</v>
       </c>
       <c r="J29">
-        <v>0.8549624558093003</v>
+        <v>0.8027521407147281</v>
       </c>
       <c r="K29">
-        <v>0.86895081679186</v>
+        <v>0.812295736041433</v>
       </c>
       <c r="L29">
-        <v>0.8867126618793689</v>
+        <v>0.8178936125936087</v>
       </c>
       <c r="M29">
-        <v>0.9022151727716896</v>
+        <v>0.8259238766309502</v>
       </c>
       <c r="N29">
-        <v>0.9209937695973014</v>
+        <v>0.833930671928019</v>
       </c>
       <c r="O29">
-        <v>0.9300449912232706</v>
+        <v>0.8401843620111038</v>
       </c>
       <c r="P29">
-        <v>0.9392182853869389</v>
+        <v>0.8477317231405177</v>
+      </c>
+      <c r="Q29">
+        <v>0.8616111200608325</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.5764631660922883</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.6330685772366783</v>
+        <v>0.5617326332096206</v>
       </c>
       <c r="D30">
-        <v>0.7070569412800431</v>
+        <v>0.6492772092810055</v>
       </c>
       <c r="E30">
-        <v>0.7220445804087592</v>
+        <v>0.7121758613489368</v>
       </c>
       <c r="F30">
-        <v>0.736347124591711</v>
+        <v>0.7443130822004882</v>
       </c>
       <c r="G30">
-        <v>0.7523754403825675</v>
+        <v>0.7646502585025683</v>
       </c>
       <c r="H30">
-        <v>0.7676336153743367</v>
+        <v>0.7681489726593559</v>
       </c>
       <c r="I30">
-        <v>0.7968056776680726</v>
+        <v>0.7707194730300099</v>
       </c>
       <c r="J30">
-        <v>0.836039810683936</v>
+        <v>0.8020887514090684</v>
       </c>
       <c r="K30">
-        <v>0.8767393367235397</v>
+        <v>0.8118517290458876</v>
       </c>
       <c r="L30">
-        <v>0.8938130587526658</v>
+        <v>0.8188242609221923</v>
       </c>
       <c r="M30">
-        <v>0.9105576950976069</v>
+        <v>0.8246677526564167</v>
       </c>
       <c r="N30">
-        <v>0.9245306684909145</v>
+        <v>0.8324776236764007</v>
       </c>
       <c r="O30">
-        <v>0.9366532067854525</v>
+        <v>0.83840469472484</v>
       </c>
       <c r="P30">
-        <v>0.9444775845437883</v>
+        <v>0.8453416261546151</v>
+      </c>
+      <c r="Q30">
+        <v>0.8582030262565086</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.5764220860086985</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.6326720572452916</v>
+        <v>0.5615728877644662</v>
       </c>
       <c r="D31">
-        <v>0.7061221462369924</v>
+        <v>0.6492629572751668</v>
       </c>
       <c r="E31">
-        <v>0.7188706651289283</v>
+        <v>0.7120123218942891</v>
       </c>
       <c r="F31">
-        <v>0.7320611164060669</v>
+        <v>0.7443018553838652</v>
       </c>
       <c r="G31">
-        <v>0.7420822335878672</v>
+        <v>0.7643228692057763</v>
       </c>
       <c r="H31">
-        <v>0.7496198421718681</v>
+        <v>0.7677639440224108</v>
       </c>
       <c r="I31">
-        <v>0.7645618824792639</v>
+        <v>0.7701734435998309</v>
       </c>
       <c r="J31">
-        <v>0.7829413444819477</v>
+        <v>0.8016084955221022</v>
       </c>
       <c r="K31">
-        <v>0.8072883557383186</v>
+        <v>0.8119392159233201</v>
       </c>
       <c r="L31">
-        <v>0.8162365574286319</v>
+        <v>0.821974516357781</v>
       </c>
       <c r="M31">
-        <v>0.8288031713837667</v>
+        <v>0.8243074450404553</v>
       </c>
       <c r="N31">
-        <v>0.8446875364025619</v>
+        <v>0.8317954243971115</v>
       </c>
       <c r="O31">
-        <v>0.8647898628110134</v>
+        <v>0.8384578720720304</v>
       </c>
       <c r="P31">
-        <v>0.872386293718881</v>
+        <v>0.8442494824229334</v>
+      </c>
+      <c r="Q31">
+        <v>0.8587443888075363</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.561883517829185</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.6492824128193501</v>
+        <v>0.5619574646871225</v>
       </c>
       <c r="D32">
-        <v>0.7123449599378485</v>
+        <v>0.6493547040117164</v>
       </c>
       <c r="E32">
-        <v>0.7443660577637363</v>
+        <v>0.7126286888585327</v>
       </c>
       <c r="F32">
-        <v>0.7650825083334859</v>
+        <v>0.7445882300654127</v>
       </c>
       <c r="G32">
-        <v>0.7686383937443441</v>
+        <v>0.7657155231184767</v>
       </c>
       <c r="H32">
-        <v>0.7714408147152574</v>
+        <v>0.7694207134441767</v>
       </c>
       <c r="I32">
-        <v>0.8026600508391477</v>
+        <v>0.7725863451736564</v>
       </c>
       <c r="J32">
-        <v>0.812263064164377</v>
+        <v>0.8038410940467612</v>
       </c>
       <c r="K32">
-        <v>0.8182323382631078</v>
+        <v>0.8136560583417821</v>
       </c>
       <c r="L32">
-        <v>0.8282229038688391</v>
+        <v>0.8202387206817841</v>
       </c>
       <c r="M32">
-        <v>0.8371239623120978</v>
+        <v>0.8324146103331069</v>
       </c>
       <c r="N32">
-        <v>0.8445600614668181</v>
+        <v>0.8435215793487669</v>
       </c>
       <c r="O32">
-        <v>0.8556317978683903</v>
+        <v>0.8543910405317805</v>
       </c>
       <c r="P32">
-        <v>0.871586390722342</v>
+        <v>0.8664490650537015</v>
+      </c>
+      <c r="Q32">
+        <v>0.8792257434977584</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.5617990615923945</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.64929951493649</v>
+        <v>0.5619416557644166</v>
       </c>
       <c r="D33">
-        <v>0.7122875054296625</v>
+        <v>0.6493481862723041</v>
       </c>
       <c r="E33">
-        <v>0.7444021544193751</v>
+        <v>0.7125962813128581</v>
       </c>
       <c r="F33">
-        <v>0.7649565376607049</v>
+        <v>0.7445786358192112</v>
       </c>
       <c r="G33">
-        <v>0.7685063675896888</v>
+        <v>0.7656533414744047</v>
       </c>
       <c r="H33">
-        <v>0.7712193204482116</v>
+        <v>0.76934086873753</v>
       </c>
       <c r="I33">
-        <v>0.8027521407147281</v>
+        <v>0.7724704173749884</v>
       </c>
       <c r="J33">
-        <v>0.812295736041433</v>
+        <v>0.8037744934427286</v>
       </c>
       <c r="K33">
-        <v>0.8178936125936087</v>
+        <v>0.813356087363903</v>
       </c>
       <c r="L33">
-        <v>0.8259238766309502</v>
+        <v>0.8195915992597653</v>
       </c>
       <c r="M33">
-        <v>0.833930671928019</v>
+        <v>0.8312302735263476</v>
       </c>
       <c r="N33">
-        <v>0.8401843620111038</v>
+        <v>0.8416762062920121</v>
       </c>
       <c r="O33">
-        <v>0.8477317231405177</v>
+        <v>0.8512081418838446</v>
       </c>
       <c r="P33">
-        <v>0.8616111200608325</v>
+        <v>0.8628264460637153</v>
+      </c>
+      <c r="Q33">
+        <v>0.87679796671292</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.5617326332096206</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.6492772092810055</v>
+        <v>0.5619212944677427</v>
       </c>
       <c r="D34">
-        <v>0.7121758613489368</v>
+        <v>0.6493656972527063</v>
       </c>
       <c r="E34">
-        <v>0.7443130822004882</v>
+        <v>0.7125823239406883</v>
       </c>
       <c r="F34">
-        <v>0.7646502585025683</v>
+        <v>0.7445796278369416</v>
       </c>
       <c r="G34">
-        <v>0.7681489726593559</v>
+        <v>0.7655732251345068</v>
       </c>
       <c r="H34">
-        <v>0.7707194730300099</v>
+        <v>0.7692339098214844</v>
       </c>
       <c r="I34">
-        <v>0.8020887514090684</v>
+        <v>0.7722913811080083</v>
       </c>
       <c r="J34">
-        <v>0.8118517290458876</v>
+        <v>0.8030819212756085</v>
       </c>
       <c r="K34">
-        <v>0.8188242609221923</v>
+        <v>0.8124430583868179</v>
       </c>
       <c r="L34">
-        <v>0.8246677526564167</v>
+        <v>0.8183703913722969</v>
       </c>
       <c r="M34">
-        <v>0.8324776236764007</v>
+        <v>0.82945175556899</v>
       </c>
       <c r="N34">
-        <v>0.83840469472484</v>
+        <v>0.8393433968797376</v>
       </c>
       <c r="O34">
-        <v>0.8453416261546151</v>
+        <v>0.8478907330859171</v>
       </c>
       <c r="P34">
-        <v>0.8582030262565086</v>
+        <v>0.85882907915032</v>
+      </c>
+      <c r="Q34">
+        <v>0.8749013515899252</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.5615728877644662</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.6492629572751668</v>
+        <v>0.5618961005982026</v>
       </c>
       <c r="D35">
-        <v>0.7120123218942891</v>
+        <v>0.6494146047784989</v>
       </c>
       <c r="E35">
-        <v>0.7443018553838652</v>
+        <v>0.712625357640863</v>
       </c>
       <c r="F35">
-        <v>0.7643228692057763</v>
+        <v>0.7446278499131933</v>
       </c>
       <c r="G35">
-        <v>0.7677639440224108</v>
+        <v>0.7655508178907818</v>
       </c>
       <c r="H35">
-        <v>0.7701734435998309</v>
+        <v>0.7692001002892996</v>
       </c>
       <c r="I35">
-        <v>0.8016084955221022</v>
+        <v>0.7722247697592346</v>
       </c>
       <c r="J35">
-        <v>0.8119392159233201</v>
+        <v>0.803104817524011</v>
       </c>
       <c r="K35">
-        <v>0.821974516357781</v>
+        <v>0.8124921633251746</v>
       </c>
       <c r="L35">
-        <v>0.8243074450404553</v>
+        <v>0.8182646710416008</v>
       </c>
       <c r="M35">
-        <v>0.8317954243971115</v>
+        <v>0.8286909148576789</v>
       </c>
       <c r="N35">
-        <v>0.8384578720720304</v>
+        <v>0.8382105381330964</v>
       </c>
       <c r="O35">
-        <v>0.8442494824229334</v>
+        <v>0.8460322086493215</v>
       </c>
       <c r="P35">
-        <v>0.8587443888075363</v>
+        <v>0.8559843841124872</v>
+      </c>
+      <c r="Q35">
+        <v>0.8721436710745364</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.5619574646871225</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.6493547040117164</v>
+        <v>0.5616035398176338</v>
       </c>
       <c r="D36">
-        <v>0.7126286888585327</v>
+        <v>0.6495085177366602</v>
       </c>
       <c r="E36">
-        <v>0.7445882300654127</v>
+        <v>0.7123225810880163</v>
       </c>
       <c r="F36">
-        <v>0.7657155231184767</v>
+        <v>0.7445226412077428</v>
       </c>
       <c r="G36">
-        <v>0.7694207134441767</v>
+        <v>0.7646285869725103</v>
       </c>
       <c r="H36">
-        <v>0.7725863451736564</v>
+        <v>0.7680858839503134</v>
       </c>
       <c r="I36">
-        <v>0.8038410940467612</v>
+        <v>0.7706178613263382</v>
       </c>
       <c r="J36">
-        <v>0.8136560583417821</v>
+        <v>0.8011776504484243</v>
       </c>
       <c r="K36">
-        <v>0.8202387206817841</v>
+        <v>0.8113511034450461</v>
       </c>
       <c r="L36">
-        <v>0.8324146103331069</v>
+        <v>0.8216879391912948</v>
       </c>
       <c r="M36">
-        <v>0.8435215793487669</v>
+        <v>0.8244819629307494</v>
       </c>
       <c r="N36">
-        <v>0.8543910405317805</v>
+        <v>0.8318100897452365</v>
       </c>
       <c r="O36">
-        <v>0.8664490650537015</v>
+        <v>0.838228416942245</v>
       </c>
       <c r="P36">
-        <v>0.8792257434977584</v>
+        <v>0.8432049388589077</v>
+      </c>
+      <c r="Q36">
+        <v>0.8581952308595516</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.5619416557644166</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.6493481862723041</v>
+        <v>0.5808959060757494</v>
       </c>
       <c r="D37">
-        <v>0.7125962813128581</v>
+        <v>0.7386256883272466</v>
       </c>
       <c r="E37">
-        <v>0.7445786358192112</v>
+        <v>0.7510790834469265</v>
       </c>
       <c r="F37">
-        <v>0.7656533414744047</v>
+        <v>0.7554584479546337</v>
       </c>
       <c r="G37">
-        <v>0.76934086873753</v>
+        <v>0.7680010302606333</v>
       </c>
       <c r="H37">
-        <v>0.7724704173749884</v>
+        <v>0.8026576500854399</v>
       </c>
       <c r="I37">
-        <v>0.8037744934427286</v>
+        <v>0.8332402014406202</v>
       </c>
       <c r="J37">
-        <v>0.813356087363903</v>
+        <v>0.8504248124951267</v>
       </c>
       <c r="K37">
-        <v>0.8195915992597653</v>
+        <v>0.8653717982045173</v>
       </c>
       <c r="L37">
-        <v>0.8312302735263476</v>
+        <v>0.8779869129101903</v>
       </c>
       <c r="M37">
-        <v>0.8416762062920121</v>
+        <v>0.8963936275234725</v>
       </c>
       <c r="N37">
-        <v>0.8512081418838446</v>
+        <v>0.9087279633128664</v>
       </c>
       <c r="O37">
-        <v>0.8628264460637153</v>
+        <v>0.916885317039115</v>
       </c>
       <c r="P37">
-        <v>0.87679796671292</v>
+        <v>0.9226513904630852</v>
+      </c>
+      <c r="Q37">
+        <v>0.9283226557861257</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.5619212944677427</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.6493656972527063</v>
+        <v>0.5819392991120622</v>
       </c>
       <c r="D38">
-        <v>0.7125823239406883</v>
+        <v>0.7367170060327375</v>
       </c>
       <c r="E38">
-        <v>0.7445796278369416</v>
+        <v>0.7393934456583859</v>
       </c>
       <c r="F38">
-        <v>0.7655732251345068</v>
+        <v>0.7471258963782219</v>
       </c>
       <c r="G38">
-        <v>0.7692339098214844</v>
+        <v>0.7559398313351462</v>
       </c>
       <c r="H38">
-        <v>0.7722913811080083</v>
+        <v>0.7799615529505463</v>
       </c>
       <c r="I38">
-        <v>0.8030819212756085</v>
+        <v>0.8189969292461328</v>
       </c>
       <c r="J38">
-        <v>0.8124430583868179</v>
+        <v>0.8287446633462818</v>
       </c>
       <c r="K38">
-        <v>0.8183703913722969</v>
+        <v>0.8470418994489691</v>
       </c>
       <c r="L38">
-        <v>0.82945175556899</v>
+        <v>0.8685106700786397</v>
       </c>
       <c r="M38">
-        <v>0.8393433968797376</v>
+        <v>0.8728757301975658</v>
       </c>
       <c r="N38">
-        <v>0.8478907330859171</v>
+        <v>0.882666420895873</v>
       </c>
       <c r="O38">
-        <v>0.85882907915032</v>
+        <v>0.8927231375741806</v>
       </c>
       <c r="P38">
-        <v>0.8749013515899252</v>
+        <v>0.9018304205360306</v>
+      </c>
+      <c r="Q38">
+        <v>0.9104511952129147</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.5618961005982026</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.6494146047784989</v>
+        <v>0.582708528388952</v>
       </c>
       <c r="D39">
-        <v>0.712625357640863</v>
+        <v>0.7354425720519417</v>
       </c>
       <c r="E39">
-        <v>0.7446278499131933</v>
+        <v>0.7377068839027311</v>
       </c>
       <c r="F39">
-        <v>0.7655508178907818</v>
+        <v>0.7443576582316327</v>
       </c>
       <c r="G39">
-        <v>0.7692001002892996</v>
+        <v>0.7643329079243611</v>
       </c>
       <c r="H39">
-        <v>0.7722247697592346</v>
+        <v>0.771341201541641</v>
       </c>
       <c r="I39">
-        <v>0.803104817524011</v>
+        <v>0.7979969786546989</v>
       </c>
       <c r="J39">
-        <v>0.8124921633251746</v>
+        <v>0.809531530443038</v>
       </c>
       <c r="K39">
-        <v>0.8182646710416008</v>
+        <v>0.821637244298573</v>
       </c>
       <c r="L39">
-        <v>0.8286909148576789</v>
+        <v>0.8355467621794791</v>
       </c>
       <c r="M39">
-        <v>0.8382105381330964</v>
+        <v>0.8478958987054417</v>
       </c>
       <c r="N39">
-        <v>0.8460322086493215</v>
+        <v>0.8609512384510466</v>
       </c>
       <c r="O39">
-        <v>0.8559843841124872</v>
+        <v>0.8718928912052224</v>
       </c>
       <c r="P39">
-        <v>0.8721436710745364</v>
+        <v>0.881171066136863</v>
+      </c>
+      <c r="Q39">
+        <v>0.8969374555197627</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.5616035398176338</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.6495085177366602</v>
+        <v>0.5491780080823562</v>
       </c>
       <c r="D40">
-        <v>0.7123225810880163</v>
+        <v>0.5939572841572275</v>
       </c>
       <c r="E40">
-        <v>0.7445226412077428</v>
+        <v>0.6718771424864383</v>
       </c>
       <c r="F40">
-        <v>0.7646285869725103</v>
+        <v>0.6816906060399914</v>
       </c>
       <c r="G40">
-        <v>0.7680858839503134</v>
+        <v>0.7436057768465072</v>
       </c>
       <c r="H40">
-        <v>0.7706178613263382</v>
+        <v>0.7776804349829023</v>
       </c>
       <c r="I40">
-        <v>0.8011776504484243</v>
+        <v>0.8010694898991086</v>
       </c>
       <c r="J40">
-        <v>0.8113511034450461</v>
+        <v>0.8170337264191742</v>
       </c>
       <c r="K40">
-        <v>0.8216879391912948</v>
+        <v>0.8361309245299009</v>
       </c>
       <c r="L40">
-        <v>0.8244819629307494</v>
+        <v>0.8544191446312371</v>
       </c>
       <c r="M40">
-        <v>0.8318100897452365</v>
+        <v>0.8703680056856673</v>
       </c>
       <c r="N40">
-        <v>0.838228416942245</v>
+        <v>0.8809527634417218</v>
       </c>
       <c r="O40">
-        <v>0.8432049388589077</v>
+        <v>0.8910655871883659</v>
       </c>
       <c r="P40">
-        <v>0.8581952308595516</v>
+        <v>0.8982708163820429</v>
+      </c>
+      <c r="Q40">
+        <v>0.9094755372184705</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.5808959060757494</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0.7386256883272466</v>
+        <v>0.5482351079432926</v>
       </c>
       <c r="D41">
-        <v>0.7510790834469265</v>
+        <v>0.610838766730469</v>
       </c>
       <c r="E41">
-        <v>0.7554584479546337</v>
+        <v>0.6628130978153519</v>
       </c>
       <c r="F41">
-        <v>0.7680010302606333</v>
+        <v>0.7008959376271178</v>
       </c>
       <c r="G41">
-        <v>0.8026576500854399</v>
+        <v>0.7511734198616612</v>
       </c>
       <c r="H41">
-        <v>0.8332402014406202</v>
+        <v>0.7907328406309906</v>
       </c>
       <c r="I41">
-        <v>0.8504248124951267</v>
+        <v>0.8066637950447183</v>
       </c>
       <c r="J41">
-        <v>0.8653717982045173</v>
+        <v>0.8272373307252215</v>
       </c>
       <c r="K41">
-        <v>0.8779869129101903</v>
+        <v>0.8463911842276438</v>
       </c>
       <c r="L41">
-        <v>0.8963936275234725</v>
+        <v>0.8758868518282199</v>
       </c>
       <c r="M41">
-        <v>0.9087279633128664</v>
+        <v>0.8886399075895679</v>
       </c>
       <c r="N41">
-        <v>0.916885317039115</v>
+        <v>0.9045630827911292</v>
       </c>
       <c r="O41">
-        <v>0.9226513904630852</v>
+        <v>0.9230595634577955</v>
       </c>
       <c r="P41">
-        <v>0.9283226557861257</v>
+        <v>0.9397080758170161</v>
+      </c>
+      <c r="Q41">
+        <v>0.9479990318687451</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.5819392991120622</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0.7367170060327375</v>
+        <v>0.4624228989424258</v>
       </c>
       <c r="D42">
-        <v>0.7393934456583859</v>
+        <v>0.5742055755976123</v>
       </c>
       <c r="E42">
-        <v>0.7471258963782219</v>
+        <v>0.6304562391282055</v>
       </c>
       <c r="F42">
-        <v>0.7559398313351462</v>
+        <v>0.6893426742063641</v>
       </c>
       <c r="G42">
-        <v>0.7799615529505463</v>
+        <v>0.7186059919491787</v>
       </c>
       <c r="H42">
-        <v>0.8189969292461328</v>
+        <v>0.729644091798318</v>
       </c>
       <c r="I42">
-        <v>0.8287446633462818</v>
+        <v>0.7659477670047983</v>
       </c>
       <c r="J42">
-        <v>0.8470418994489691</v>
+        <v>0.7881063761043453</v>
       </c>
       <c r="K42">
-        <v>0.8685106700786397</v>
+        <v>0.8100457907140776</v>
       </c>
       <c r="L42">
-        <v>0.8728757301975658</v>
+        <v>0.8466402756523517</v>
       </c>
       <c r="M42">
-        <v>0.882666420895873</v>
+        <v>0.8693599811239459</v>
       </c>
       <c r="N42">
-        <v>0.8927231375741806</v>
+        <v>0.9062073640146512</v>
       </c>
       <c r="O42">
-        <v>0.9018304205360306</v>
+        <v>0.9163848344292982</v>
       </c>
       <c r="P42">
-        <v>0.9104511952129147</v>
+        <v>0.9245328292667597</v>
+      </c>
+      <c r="Q42">
+        <v>0.9324934542251804</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.582708528388952</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.7354425720519417</v>
+        <v>0.5614771258061865</v>
       </c>
       <c r="D43">
-        <v>0.7377068839027311</v>
+        <v>0.6130140320174605</v>
       </c>
       <c r="E43">
-        <v>0.7443576582316327</v>
+        <v>0.6451621083984057</v>
       </c>
       <c r="F43">
-        <v>0.7643329079243611</v>
+        <v>0.684483849045865</v>
       </c>
       <c r="G43">
-        <v>0.771341201541641</v>
+        <v>0.7542106251329661</v>
       </c>
       <c r="H43">
-        <v>0.7979969786546989</v>
+        <v>0.7792038780039068</v>
       </c>
       <c r="I43">
-        <v>0.809531530443038</v>
+        <v>0.7938594783616929</v>
       </c>
       <c r="J43">
-        <v>0.821637244298573</v>
+        <v>0.8262660577804759</v>
       </c>
       <c r="K43">
-        <v>0.8355467621794791</v>
+        <v>0.8572739645464341</v>
       </c>
       <c r="L43">
-        <v>0.8478958987054417</v>
+        <v>0.8774707720858864</v>
       </c>
       <c r="M43">
-        <v>0.8609512384510466</v>
+        <v>0.9005714562504953</v>
       </c>
       <c r="N43">
-        <v>0.8718928912052224</v>
+        <v>0.9176681294846332</v>
       </c>
       <c r="O43">
-        <v>0.881171066136863</v>
+        <v>0.9264619294634846</v>
       </c>
       <c r="P43">
-        <v>0.8969374555197627</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.5491780080823562</v>
-      </c>
-      <c r="C44">
-        <v>0.5939572841572275</v>
-      </c>
-      <c r="D44">
-        <v>0.6718771424864383</v>
-      </c>
-      <c r="E44">
-        <v>0.6816906060399914</v>
-      </c>
-      <c r="F44">
-        <v>0.7436057768465072</v>
-      </c>
-      <c r="G44">
-        <v>0.7776804349829023</v>
-      </c>
-      <c r="H44">
-        <v>0.8010694898991086</v>
-      </c>
-      <c r="I44">
-        <v>0.8170337264191742</v>
-      </c>
-      <c r="J44">
-        <v>0.8361309245299009</v>
-      </c>
-      <c r="K44">
-        <v>0.8544191446312371</v>
-      </c>
-      <c r="L44">
-        <v>0.8703680056856673</v>
-      </c>
-      <c r="M44">
-        <v>0.8809527634417218</v>
-      </c>
-      <c r="N44">
-        <v>0.8910655871883659</v>
-      </c>
-      <c r="O44">
-        <v>0.8982708163820429</v>
-      </c>
-      <c r="P44">
-        <v>0.9094755372184705</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.5482351079432926</v>
-      </c>
-      <c r="C45">
-        <v>0.610838766730469</v>
-      </c>
-      <c r="D45">
-        <v>0.6628130978153519</v>
-      </c>
-      <c r="E45">
-        <v>0.7008959376271178</v>
-      </c>
-      <c r="F45">
-        <v>0.7511734198616612</v>
-      </c>
-      <c r="G45">
-        <v>0.7907328406309906</v>
-      </c>
-      <c r="H45">
-        <v>0.8066637950447183</v>
-      </c>
-      <c r="I45">
-        <v>0.8272373307252215</v>
-      </c>
-      <c r="J45">
-        <v>0.8463911842276438</v>
-      </c>
-      <c r="K45">
-        <v>0.8758868518282199</v>
-      </c>
-      <c r="L45">
-        <v>0.8886399075895679</v>
-      </c>
-      <c r="M45">
-        <v>0.9045630827911292</v>
-      </c>
-      <c r="N45">
-        <v>0.9230595634577955</v>
-      </c>
-      <c r="O45">
-        <v>0.9397080758170161</v>
-      </c>
-      <c r="P45">
-        <v>0.9479990318687451</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.4624228989424258</v>
-      </c>
-      <c r="C46">
-        <v>0.5742055755976123</v>
-      </c>
-      <c r="D46">
-        <v>0.6304562391282055</v>
-      </c>
-      <c r="E46">
-        <v>0.6893426742063641</v>
-      </c>
-      <c r="F46">
-        <v>0.7186059919491787</v>
-      </c>
-      <c r="G46">
-        <v>0.729644091798318</v>
-      </c>
-      <c r="H46">
-        <v>0.7659477670047983</v>
-      </c>
-      <c r="I46">
-        <v>0.7881063761043453</v>
-      </c>
-      <c r="J46">
-        <v>0.8100457907140776</v>
-      </c>
-      <c r="K46">
-        <v>0.8466402756523517</v>
-      </c>
-      <c r="L46">
-        <v>0.8693599811239459</v>
-      </c>
-      <c r="M46">
-        <v>0.9062073640146512</v>
-      </c>
-      <c r="N46">
-        <v>0.9163848344292982</v>
-      </c>
-      <c r="O46">
-        <v>0.9245328292667597</v>
-      </c>
-      <c r="P46">
-        <v>0.9324934542251804</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.5614771258061865</v>
-      </c>
-      <c r="C47">
-        <v>0.6130140320174605</v>
-      </c>
-      <c r="D47">
-        <v>0.6451621083984057</v>
-      </c>
-      <c r="E47">
-        <v>0.684483849045865</v>
-      </c>
-      <c r="F47">
-        <v>0.7542106251329661</v>
-      </c>
-      <c r="G47">
-        <v>0.7792038780039068</v>
-      </c>
-      <c r="H47">
-        <v>0.7938594783616929</v>
-      </c>
-      <c r="I47">
-        <v>0.8262660577804759</v>
-      </c>
-      <c r="J47">
-        <v>0.8572739645464341</v>
-      </c>
-      <c r="K47">
-        <v>0.8774707720858864</v>
-      </c>
-      <c r="L47">
-        <v>0.9005714562504953</v>
-      </c>
-      <c r="M47">
-        <v>0.9176681294846332</v>
-      </c>
-      <c r="N47">
-        <v>0.9264619294634846</v>
-      </c>
-      <c r="O47">
         <v>0.9384421732540003</v>
       </c>
-      <c r="P47">
+      <c r="Q43">
         <v>0.9495482625765738</v>
       </c>
     </row>
